--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 09:45</t>
+          <t>2026-09-20 09:47</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -457,15 +457,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -491,10 +493,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Data Pool (GB)</t>
+          <t>Base Pool (GB)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Add-ons (GB)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total Pool (GB)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -518,7 +530,13 @@
       <c r="E2" s="4" t="n">
         <v>18350</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>18350</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>seeded</t>
         </is>
@@ -542,7 +560,13 @@
       <c r="E3" s="4" t="n">
         <v>18350</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>35350</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>seeded</t>
         </is>
@@ -566,9 +590,15 @@
       <c r="E4" s="4" t="n">
         <v>17700</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:47</t>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>17700</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:55</t>
         </is>
       </c>
     </row>
@@ -603,7 +633,14 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data Pool is the kit count x 50 GB base allotment; it does not include data add-ons.</t>
+          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Purchased On date falls inside that cycle. Total Pool is the two added together.</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 09:55</t>
+          <t>2026-09-20 09:58</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>238</v>
@@ -588,17 +588,17 @@
         <v>34140.33</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>17700</v>
+        <v>18350</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>17700</v>
+        <v>18350</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 09:58</t>
+          <t>corrected to 367</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,47 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>A cycle's Data Used only ever increases. If a later Granite export reports a lower</t>
+          <t>A cycle's Data Used, Kits and Base Pool only ever increase. If a later Granite</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>figure for a month already recorded here, the higher recorded figure is kept.</t>
+          <t>export reports lower figures for a month already recorded here, the higher</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+          <t>recorded figures are kept. Genuinely higher figures always write through, so the</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>record corrects itself if their report recovers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>If kits are ever genuinely retired, edit the affected rows by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Purchased On date falls inside that cycle. Total Pool is the two added together.</t>
         </is>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -531,10 +531,10 @@
         <v>18350</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>18350</v>
+        <v>33350</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -591,14 +591,14 @@
         <v>18350</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>18350</v>
+        <v>38350</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>corrected to 367</t>
+          <t>2026-09-20 12:15</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -585,7 +585,7 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34140.33</v>
+        <v>34260.05</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>18350</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 12:15</t>
+          <t>2026-09-20 12:29</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -585,7 +585,7 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34260.05</v>
+        <v>35591.02</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>18350</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 12:29</t>
+          <t>2026-09-21 10:13</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -457,17 +457,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -493,20 +495,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Gen 3 Used (GB)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mini Used (GB)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Base Pool (GB)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Add-ons (GB)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total Pool (GB)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -527,16 +539,22 @@
       <c r="D2" s="3" t="n">
         <v>32161.76</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
+        <v>21987.67</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>10174.09</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>18350</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>33350</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>seeded</t>
         </is>
@@ -557,16 +575,18 @@
       <c r="D3" s="3" t="n">
         <v>34683.3</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="n">
         <v>18350</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>17000</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>35350</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>seeded</t>
         </is>
@@ -587,18 +607,24 @@
       <c r="D4" s="3" t="n">
         <v>35591.02</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
+        <v>16587.62</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>19003.4</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>18350</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>38350</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 10:13</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:34</t>
         </is>
       </c>
     </row>
@@ -654,12 +680,33 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+          <t>Gen 3 and Mini Used follow the same rule. Data Used is never less than the two</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>added together. A past cycle without a split is back-filled from the export only</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>when the export total for that cycle matches the recorded total; otherwise blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Purchased On date falls inside that cycle. Total Pool is the two added together.</t>
         </is>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -605,13 +605,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35591.02</v>
+        <v>35751.98</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>16587.62</v>
+        <v>16673.73</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19003.4</v>
+        <v>19078.25</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -624,7 +624,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 15:34</t>
+          <t>2026-09-21 15:35</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -575,8 +575,12 @@
       <c r="D3" s="3" t="n">
         <v>34683.3</v>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+      <c r="E3" s="3" t="n">
+        <v>20370.05</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>13551.66</v>
+      </c>
       <c r="G3" s="4" t="n">
         <v>18350</v>
       </c>
@@ -687,14 +691,14 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>added together. A past cycle without a split is back-filled from the export only</t>
+          <t>added together. A past cycle without a split is back-filled from the export; any</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>when the export total for that cycle matches the recorded total; otherwise blank.</t>
+          <t>part of the recorded total the export no longer has is shown as not split.</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35751.98</v>
+        <v>36136.74</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>16673.73</v>
+        <v>16849.86</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19078.25</v>
+        <v>19286.88</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 15:35</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36136.74</v>
+        <v>36890.96</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>16849.86</v>
+        <v>17236.7</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19286.88</v>
+        <v>19654.26</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>36890.96</v>
+        <v>37118.36</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>17236.7</v>
+        <v>17364.62</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19654.26</v>
+        <v>19753.74</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37118.36</v>
+        <v>39022.57</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>17364.62</v>
+        <v>18315.94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19753.74</v>
+        <v>20706.63</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39022.57</v>
+        <v>39322.79</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18315.94</v>
+        <v>18475.22</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>20706.63</v>
+        <v>20847.57</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -621,14 +621,14 @@
         <v>18350</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>20000</v>
+        <v>32000</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>38350</v>
+        <v>50350</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 07:56</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39322.79</v>
+        <v>39628</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18475.22</v>
+        <v>18658.05</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>20847.57</v>
+        <v>20969.95</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39628</v>
+        <v>40258.6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18658.05</v>
+        <v>18952.42</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>20969.95</v>
+        <v>21306.18</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40258.6</v>
+        <v>40616.42</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18952.42</v>
+        <v>19131.95</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>21306.18</v>
+        <v>21484.47</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40616.42</v>
+        <v>41604.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19131.95</v>
+        <v>19657.89</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>21484.47</v>
+        <v>21946.61</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>41604.5</v>
+        <v>41980.87</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19657.89</v>
+        <v>19873.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>21946.61</v>
+        <v>22107.07</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>41980.87</v>
+        <v>42498.28</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19873.8</v>
+        <v>20132.4</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>22107.07</v>
+        <v>22365.88</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>42498.28</v>
+        <v>43709.77</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20132.4</v>
+        <v>20713.75</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>22365.88</v>
+        <v>22996.02</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>43709.77</v>
+        <v>44286.18</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20713.75</v>
+        <v>20952.28</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>22996.02</v>
+        <v>23333.9</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44286.18</v>
+        <v>44575.64</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20952.28</v>
+        <v>21119.07</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23333.9</v>
+        <v>23456.57</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44575.64</v>
+        <v>44712.26</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>21119.07</v>
+        <v>21198.31</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23456.57</v>
+        <v>23513.95</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44712.26</v>
+        <v>45753.58</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>21198.31</v>
+        <v>21696.13</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23513.95</v>
+        <v>24057.45</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>45753.58</v>
+        <v>45953.96</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>21696.13</v>
+        <v>21818.75</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24057.45</v>
+        <v>24135.21</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>45953.96</v>
+        <v>46840.01</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>21818.75</v>
+        <v>22277.75</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24135.21</v>
+        <v>24562.26</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46840.01</v>
+        <v>46857.07</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>22277.75</v>
+        <v>22282.49</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24562.26</v>
+        <v>24574.58</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46857.07</v>
+        <v>47246.89</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>22282.49</v>
+        <v>22504.02</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24574.58</v>
+        <v>24742.87</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -609,13 +609,13 @@
         <v>238</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>47246.89</v>
+        <v>47530.35</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>22504.02</v>
+        <v>22620.22</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24742.87</v>
+        <v>24910.13</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18350</v>
@@ -628,89 +628,146 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 17:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+          <t>2026-09-30 23:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>17700</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>17700</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>One row per billing cycle, written by build_starlink_usage.py on every run.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>A cycle's Data Used, Kits and Base Pool only ever increase. If a later Granite</t>
+          <t>One row per billing cycle, written by build_starlink_usage.py on every run.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>export reports lower figures for a month already recorded here, the higher</t>
+          <t>A cycle's Data Used, Kits and Base Pool only ever increase. If a later Granite</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>recorded figures are kept. Genuinely higher figures always write through, so the</t>
+          <t>export reports lower figures for a month already recorded here, the higher</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>record corrects itself if their report recovers.</t>
+          <t>recorded figures are kept. Genuinely higher figures always write through, so the</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>If kits are ever genuinely retired, edit the affected rows by hand.</t>
+          <t>record corrects itself if their report recovers.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Gen 3 and Mini Used follow the same rule. Data Used is never less than the two</t>
+          <t>If kits are ever genuinely retired, edit the affected rows by hand.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>added together. A past cycle without a split is back-filled from the export; any</t>
+          <t>Gen 3 and Mini Used follow the same rule. Data Used is never less than the two</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>part of the recorded total the export no longer has is shown as not split.</t>
+          <t>added together. A past cycle without a split is back-filled from the export; any</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+          <t>part of the recorded total the export no longer has is shown as not split.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Past cycles are also refreshed from the export on every run, upward only. The</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>export keeps every billing period, so a run made after a cycle rolls over still</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>picks up usage that landed after the last run inside that cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Base Pool is the kit count x 50 GB allotment. Add-ons are data purchases whose</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Purchased On date falls inside that cycle. Total Pool is the two added together.</t>
         </is>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>1356.09</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>53.88</v>
+        <v>607.8099999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>37.22</v>
+        <v>748.28</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1356.09</v>
+        <v>4509.79</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>607.8099999999999</v>
+        <v>1721.86</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>748.28</v>
+        <v>2787.93</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4509.79</v>
+        <v>6826.33</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1721.86</v>
+        <v>2450.66</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2787.93</v>
+        <v>4375.67</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 11:34</t>
+          <t>2026-10-08 08:41</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6826.33</v>
+        <v>8359.66</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2450.66</v>
+        <v>2830.44</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4375.67</v>
+        <v>5529.22</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 08:41</t>
+          <t>2026-10-10 08:31</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>142</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8359.66</v>
+        <v>9076.370000000001</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2830.44</v>
+        <v>3002.07</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5529.22</v>
+        <v>6074.3</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 08:31</t>
+          <t>2026-10-11 10:45</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>142</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>9076.370000000001</v>
+        <v>9937.1</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3002.07</v>
+        <v>3287.95</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6074.3</v>
+        <v>6649.15</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 10:45</t>
+          <t>2026-10-12 13:39</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>9937.1</v>
+        <v>10424.33</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3287.95</v>
+        <v>3439.23</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6649.15</v>
+        <v>6985.1</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 13:39</t>
+          <t>2026-10-13 09:53</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10424.33</v>
+        <v>10943.01</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3439.23</v>
+        <v>3630.68</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6985.1</v>
+        <v>7312.33</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:53</t>
+          <t>2026-10-14 09:53</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10943.01</v>
+        <v>11423.93</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3630.68</v>
+        <v>3769.92</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7312.33</v>
+        <v>7654.01</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:53</t>
+          <t>2026-10-15 10:05</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>152</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11423.93</v>
+        <v>11946.92</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3769.92</v>
+        <v>3895.11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7654.01</v>
+        <v>8051.81</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:05</t>
+          <t>2026-10-16 15:01</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>152</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11946.92</v>
+        <v>12744.35</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3895.11</v>
+        <v>4062.91</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8051.81</v>
+        <v>8681.440000000001</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:01</t>
+          <t>2026-10-19 09:26</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>152</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12744.35</v>
+        <v>12751.23</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4062.91</v>
+        <v>4064.16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8681.440000000001</v>
+        <v>8687.07</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:26</t>
+          <t>2026-10-19 13:31</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -642,16 +642,16 @@
         <v>354</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12751.23</v>
+        <v>13042.87</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4064.16</v>
+        <v>4107.28</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8687.07</v>
+        <v>8935.59</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:31</t>
+          <t>2026-10-22 11:09</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13042.87</v>
+        <v>13068.94</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4107.28</v>
+        <v>4108.27</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8935.59</v>
+        <v>8960.67</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 11:09</t>
+          <t>2026-10-22 17:37</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13068.94</v>
+        <v>13104.53</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4108.27</v>
+        <v>4111.09</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8960.67</v>
+        <v>8993.440000000001</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 17:37</t>
+          <t>2026-10-23 11:39</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13104.53</v>
+        <v>13117.87</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4111.09</v>
+        <v>4112.49</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8993.440000000001</v>
+        <v>9005.379999999999</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 11:39</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13117.87</v>
+        <v>13454.87</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4112.49</v>
+        <v>4156.11</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9005.379999999999</v>
+        <v>9298.76</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15</t>
+          <t>2026-10-26 10:31</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13454.87</v>
+        <v>13530.32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4156.11</v>
+        <v>4182.43</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9298.76</v>
+        <v>9347.889999999999</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:31</t>
+          <t>2026-10-27 16:11</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,13 +645,13 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13530.32</v>
+        <v>13556.09</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4182.43</v>
+        <v>4205.41</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9347.889999999999</v>
+        <v>9350.68</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>17700</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 16:11</t>
+          <t>2026-10-28 12:24</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,10 +645,10 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13556.09</v>
+        <v>13581.01</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4205.41</v>
+        <v>4230.33</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>9350.68</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 12:24</t>
+          <t>2026-10-29 15:42</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,10 +645,10 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13581.01</v>
+        <v>13627.2</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4230.33</v>
+        <v>4276.52</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>9350.68</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:42</t>
+          <t>2026-10-30 22:24</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_History.xlsx
+++ b/Starlink_Usage_History.xlsx
@@ -645,10 +645,10 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13627.2</v>
+        <v>13638.78</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4276.52</v>
+        <v>4288.1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>9350.68</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 22:24</t>
+          <t>2026-10-31 11:48</t>
         </is>
       </c>
     </row>
